--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414825</v>
+        <v>127414821</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817751</v>
+        <v>817880</v>
       </c>
       <c r="R9" t="n">
-        <v>7389639</v>
+        <v>7389629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127414821</v>
+        <v>127414825</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>97339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817880</v>
+        <v>817751</v>
       </c>
       <c r="R11" t="n">
-        <v>7389629</v>
+        <v>7389639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127414818</v>
+        <v>127415012</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817842</v>
+        <v>817808</v>
       </c>
       <c r="R14" t="n">
-        <v>7389499</v>
+        <v>7389634</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2078,32 +2078,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415012</v>
+        <v>127414818</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817808</v>
+        <v>817842</v>
       </c>
       <c r="R15" t="n">
-        <v>7389634</v>
+        <v>7389499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127414819</v>
+        <v>127415011</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817706</v>
+        <v>817954</v>
       </c>
       <c r="R16" t="n">
-        <v>7389394</v>
+        <v>7389688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415011</v>
+        <v>127414819</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817954</v>
+        <v>817706</v>
       </c>
       <c r="R17" t="n">
-        <v>7389688</v>
+        <v>7389394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414823</v>
+        <v>127414824</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>97339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817829</v>
+        <v>817729</v>
       </c>
       <c r="R18" t="n">
-        <v>7389658</v>
+        <v>7389647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414817</v>
+        <v>127414823</v>
       </c>
       <c r="B19" t="n">
-        <v>80152</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817848</v>
+        <v>817829</v>
       </c>
       <c r="R19" t="n">
-        <v>7389513</v>
+        <v>7389658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414824</v>
+        <v>127414817</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>80152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817729</v>
+        <v>817848</v>
       </c>
       <c r="R20" t="n">
-        <v>7389647</v>
+        <v>7389513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2717,7 @@
         <v>127414827</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127414816</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414821</v>
+        <v>127414815</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817880</v>
+        <v>817858</v>
       </c>
       <c r="R9" t="n">
-        <v>7389629</v>
+        <v>7389527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414815</v>
+        <v>127414821</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817858</v>
+        <v>817880</v>
       </c>
       <c r="R10" t="n">
-        <v>7389527</v>
+        <v>7389629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>127414825</v>
       </c>
       <c r="B11" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>127414822</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>127415010</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415012</v>
+        <v>127414818</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817808</v>
+        <v>817842</v>
       </c>
       <c r="R14" t="n">
-        <v>7389634</v>
+        <v>7389499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2078,32 +2078,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127414818</v>
+        <v>127415012</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817842</v>
+        <v>817808</v>
       </c>
       <c r="R15" t="n">
-        <v>7389499</v>
+        <v>7389634</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415011</v>
+        <v>127414819</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817954</v>
+        <v>817706</v>
       </c>
       <c r="R16" t="n">
-        <v>7389688</v>
+        <v>7389394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127414819</v>
+        <v>127415011</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>98376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817706</v>
+        <v>817954</v>
       </c>
       <c r="R17" t="n">
-        <v>7389394</v>
+        <v>7389688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414824</v>
+        <v>127414823</v>
       </c>
       <c r="B18" t="n">
-        <v>97339</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817729</v>
+        <v>817829</v>
       </c>
       <c r="R18" t="n">
-        <v>7389647</v>
+        <v>7389658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414823</v>
+        <v>127414817</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>80155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817829</v>
+        <v>817848</v>
       </c>
       <c r="R19" t="n">
-        <v>7389658</v>
+        <v>7389513</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,32 +2608,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414817</v>
+        <v>127414827</v>
       </c>
       <c r="B20" t="n">
-        <v>80152</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817848</v>
+        <v>817709</v>
       </c>
       <c r="R20" t="n">
-        <v>7389513</v>
+        <v>7389634</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414827</v>
+        <v>127414824</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>97342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817709</v>
+        <v>817729</v>
       </c>
       <c r="R21" t="n">
-        <v>7389634</v>
+        <v>7389647</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>127415013</v>
       </c>
       <c r="B22" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>127414816</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>127414815</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414821</v>
+        <v>127414825</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>97350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817880</v>
+        <v>817751</v>
       </c>
       <c r="R10" t="n">
-        <v>7389629</v>
+        <v>7389639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127414825</v>
+        <v>127414821</v>
       </c>
       <c r="B11" t="n">
-        <v>97342</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817751</v>
+        <v>817880</v>
       </c>
       <c r="R11" t="n">
-        <v>7389639</v>
+        <v>7389629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>127414822</v>
       </c>
       <c r="B12" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>127415010</v>
       </c>
       <c r="B13" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>127414818</v>
       </c>
       <c r="B14" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127415012</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>127414819</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127415011</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414823</v>
+        <v>127414824</v>
       </c>
       <c r="B18" t="n">
-        <v>80126</v>
+        <v>97350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817829</v>
+        <v>817729</v>
       </c>
       <c r="R18" t="n">
-        <v>7389658</v>
+        <v>7389647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414817</v>
+        <v>127414823</v>
       </c>
       <c r="B19" t="n">
-        <v>80155</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817848</v>
+        <v>817829</v>
       </c>
       <c r="R19" t="n">
-        <v>7389513</v>
+        <v>7389658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,32 +2608,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414827</v>
+        <v>127414817</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>80161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817709</v>
+        <v>817848</v>
       </c>
       <c r="R20" t="n">
-        <v>7389634</v>
+        <v>7389513</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414824</v>
+        <v>127414827</v>
       </c>
       <c r="B21" t="n">
-        <v>97342</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817729</v>
+        <v>817709</v>
       </c>
       <c r="R21" t="n">
-        <v>7389647</v>
+        <v>7389634</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>127415013</v>
       </c>
       <c r="B22" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414815</v>
+        <v>127414821</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817858</v>
+        <v>817880</v>
       </c>
       <c r="R9" t="n">
-        <v>7389527</v>
+        <v>7389629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414825</v>
+        <v>127414815</v>
       </c>
       <c r="B10" t="n">
-        <v>97350</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817751</v>
+        <v>817858</v>
       </c>
       <c r="R10" t="n">
-        <v>7389639</v>
+        <v>7389527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127414821</v>
+        <v>127414825</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>97351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817880</v>
+        <v>817751</v>
       </c>
       <c r="R11" t="n">
-        <v>7389629</v>
+        <v>7389639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
         <v>127415012</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127415011</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414824</v>
+        <v>127414823</v>
       </c>
       <c r="B18" t="n">
-        <v>97350</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817729</v>
+        <v>817829</v>
       </c>
       <c r="R18" t="n">
-        <v>7389647</v>
+        <v>7389658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414823</v>
+        <v>127414817</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817829</v>
+        <v>817848</v>
       </c>
       <c r="R19" t="n">
-        <v>7389658</v>
+        <v>7389513</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414817</v>
+        <v>127414824</v>
       </c>
       <c r="B20" t="n">
-        <v>80161</v>
+        <v>97351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817848</v>
+        <v>817729</v>
       </c>
       <c r="R20" t="n">
-        <v>7389513</v>
+        <v>7389647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2717,7 @@
         <v>127414827</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414821</v>
+        <v>127414815</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817880</v>
+        <v>817858</v>
       </c>
       <c r="R9" t="n">
-        <v>7389629</v>
+        <v>7389527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414815</v>
+        <v>127414821</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817858</v>
+        <v>817880</v>
       </c>
       <c r="R10" t="n">
-        <v>7389527</v>
+        <v>7389629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127414819</v>
+        <v>127415011</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>98385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817706</v>
+        <v>817954</v>
       </c>
       <c r="R16" t="n">
-        <v>7389394</v>
+        <v>7389688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415011</v>
+        <v>127414819</v>
       </c>
       <c r="B17" t="n">
-        <v>98385</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817954</v>
+        <v>817706</v>
       </c>
       <c r="R17" t="n">
-        <v>7389688</v>
+        <v>7389394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414823</v>
+        <v>127414817</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817829</v>
+        <v>817848</v>
       </c>
       <c r="R18" t="n">
-        <v>7389658</v>
+        <v>7389513</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414817</v>
+        <v>127414823</v>
       </c>
       <c r="B19" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817848</v>
+        <v>817829</v>
       </c>
       <c r="R19" t="n">
-        <v>7389513</v>
+        <v>7389658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,32 +2608,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414824</v>
+        <v>127414827</v>
       </c>
       <c r="B20" t="n">
-        <v>97351</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817729</v>
+        <v>817709</v>
       </c>
       <c r="R20" t="n">
-        <v>7389647</v>
+        <v>7389634</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414827</v>
+        <v>127414824</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>97351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817709</v>
+        <v>817729</v>
       </c>
       <c r="R21" t="n">
-        <v>7389634</v>
+        <v>7389647</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414815</v>
+        <v>127414821</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817858</v>
+        <v>817880</v>
       </c>
       <c r="R9" t="n">
-        <v>7389527</v>
+        <v>7389629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414821</v>
+        <v>127414815</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817880</v>
+        <v>817858</v>
       </c>
       <c r="R10" t="n">
-        <v>7389629</v>
+        <v>7389527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>127414825</v>
       </c>
       <c r="B11" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127414818</v>
+        <v>127415012</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817842</v>
+        <v>817808</v>
       </c>
       <c r="R14" t="n">
-        <v>7389499</v>
+        <v>7389634</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2078,32 +2078,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415012</v>
+        <v>127414818</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817808</v>
+        <v>817842</v>
       </c>
       <c r="R15" t="n">
-        <v>7389634</v>
+        <v>7389499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2187,7 +2187,7 @@
         <v>127415011</v>
       </c>
       <c r="B16" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414817</v>
+        <v>127414824</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>97352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817848</v>
+        <v>817729</v>
       </c>
       <c r="R18" t="n">
-        <v>7389513</v>
+        <v>7389647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414823</v>
+        <v>127414827</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817829</v>
+        <v>817709</v>
       </c>
       <c r="R19" t="n">
-        <v>7389658</v>
+        <v>7389634</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,32 +2608,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414827</v>
+        <v>127414817</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817709</v>
+        <v>817848</v>
       </c>
       <c r="R20" t="n">
-        <v>7389634</v>
+        <v>7389513</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414824</v>
+        <v>127414823</v>
       </c>
       <c r="B21" t="n">
-        <v>97351</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817729</v>
+        <v>817829</v>
       </c>
       <c r="R21" t="n">
-        <v>7389647</v>
+        <v>7389658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>127414820</v>
       </c>
       <c r="B8" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>127414821</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>127414825</v>
       </c>
       <c r="B11" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415012</v>
+        <v>127414818</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817808</v>
+        <v>817842</v>
       </c>
       <c r="R14" t="n">
-        <v>7389634</v>
+        <v>7389499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2078,32 +2078,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127414818</v>
+        <v>127415012</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817842</v>
+        <v>817808</v>
       </c>
       <c r="R15" t="n">
-        <v>7389499</v>
+        <v>7389634</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2187,7 +2187,7 @@
         <v>127415011</v>
       </c>
       <c r="B16" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414824</v>
+        <v>127414817</v>
       </c>
       <c r="B18" t="n">
-        <v>97352</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817729</v>
+        <v>817848</v>
       </c>
       <c r="R18" t="n">
-        <v>7389647</v>
+        <v>7389513</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414827</v>
+        <v>127414823</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817709</v>
+        <v>817829</v>
       </c>
       <c r="R19" t="n">
-        <v>7389634</v>
+        <v>7389658</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414817</v>
+        <v>127414824</v>
       </c>
       <c r="B20" t="n">
-        <v>80161</v>
+        <v>97353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817848</v>
+        <v>817729</v>
       </c>
       <c r="R20" t="n">
-        <v>7389513</v>
+        <v>7389647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414823</v>
+        <v>127414827</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817829</v>
+        <v>817709</v>
       </c>
       <c r="R21" t="n">
-        <v>7389658</v>
+        <v>7389634</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 40208-2025 artfynd.xlsx
+++ b/artfynd/A 40208-2025 artfynd.xlsx
@@ -1442,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414821</v>
+        <v>127414815</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817880</v>
+        <v>817858</v>
       </c>
       <c r="R9" t="n">
-        <v>7389629</v>
+        <v>7389527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414815</v>
+        <v>127414821</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817858</v>
+        <v>817880</v>
       </c>
       <c r="R10" t="n">
-        <v>7389527</v>
+        <v>7389629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415011</v>
+        <v>127414819</v>
       </c>
       <c r="B16" t="n">
-        <v>98387</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817954</v>
+        <v>817706</v>
       </c>
       <c r="R16" t="n">
-        <v>7389688</v>
+        <v>7389394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127414819</v>
+        <v>127415011</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>98387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817706</v>
+        <v>817954</v>
       </c>
       <c r="R17" t="n">
-        <v>7389394</v>
+        <v>7389688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414817</v>
+        <v>127414827</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817848</v>
+        <v>817709</v>
       </c>
       <c r="R18" t="n">
-        <v>7389513</v>
+        <v>7389634</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127414823</v>
+        <v>127414824</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>97353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817829</v>
+        <v>817729</v>
       </c>
       <c r="R19" t="n">
-        <v>7389658</v>
+        <v>7389647</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,32 +2608,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127414824</v>
+        <v>127414823</v>
       </c>
       <c r="B20" t="n">
-        <v>97353</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817729</v>
+        <v>817829</v>
       </c>
       <c r="R20" t="n">
-        <v>7389647</v>
+        <v>7389658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,32 +2714,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127414827</v>
+        <v>127414817</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817709</v>
+        <v>817848</v>
       </c>
       <c r="R21" t="n">
-        <v>7389634</v>
+        <v>7389513</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
